--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134434150</v>
+        <v>135472599</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477280</v>
+        <v>477064</v>
       </c>
       <c r="R2" t="n">
-        <v>6846558</v>
+        <v>6846743</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +765,440 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135472527</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>477051</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6846746</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134434150</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477280</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6846558</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135472384</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476859</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6846742</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135472967</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477362</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135472599</v>
+        <v>135482750</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+          <t>Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477064</v>
+        <v>477473</v>
       </c>
       <c r="R2" t="n">
-        <v>6846743</v>
+        <v>6846554</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135472527</v>
+        <v>135472599</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,51 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477051</v>
+        <v>477064</v>
       </c>
       <c r="R3" t="n">
-        <v>6846746</v>
+        <v>6846743</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,48 +874,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134434150</v>
+        <v>135472527</v>
       </c>
       <c r="B4" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477280</v>
+        <v>477051</v>
       </c>
       <c r="R4" t="n">
-        <v>6846558</v>
+        <v>6846746</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,17 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,66 +973,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135472384</v>
+        <v>134434150</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476859</v>
+        <v>477280</v>
       </c>
       <c r="R5" t="n">
-        <v>6846742</v>
+        <v>6846558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,12 +1050,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,19 +1075,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135472967</v>
+        <v>135472384</v>
       </c>
       <c r="B6" t="n">
         <v>99195</v>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1136,17 +1127,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477362</v>
+        <v>476859</v>
       </c>
       <c r="R6" t="n">
-        <v>6846653</v>
+        <v>6846742</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,6 +1190,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135472967</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477362</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6846653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135482750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134434150</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472384</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,8 +1326,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135482750</v>
       </c>
       <c r="B2" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135472599</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135472527</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>135472384</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135472967</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135482750</v>
       </c>
       <c r="B2" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>135472384</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135472967</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134434150</v>
+        <v>135482750</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Peslaskorpskojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477280</v>
+        <v>477473</v>
       </c>
       <c r="R2" t="n">
-        <v>6846558</v>
+        <v>6846554</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +765,581 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135482750</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135472599</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>477064</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6846743</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472599</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135472527</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477051</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6846746</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472527</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134434150</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477280</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6846558</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134434150</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135472384</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476859</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846742</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472384</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135472967</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Peslaskorpskojan, Peslaskorpskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477362</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6846653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472967</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27605-2026 artfynd.xlsx
+++ b/artfynd/A 27605-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135482750</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>135472384</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>135472967</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
